--- a/survey_templates/046_volunteer_experience_survey_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/046_volunteer_experience_survey_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'participant'}</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'participant'}</t>
+          <t>participant</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
